--- a/sofood/consegne.xlsx
+++ b/sofood/consegne.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\baron\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\baron\Desktop\PRODOTTI SOFOOD\sofood\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E81C60EA-35FD-447A-BFDE-CE8093DFA087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E828A7B8-DBA4-49E2-A01D-469B299DF441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="26">
   <si>
     <t>ZONA (ID)</t>
   </si>
@@ -95,12 +95,18 @@
   </si>
   <si>
     <t>IN CASO DI ORDINE MINIMO NON RISPETTATO</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 400€ (spedizione non disponibile per ordini inferiori a 250€)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="6" formatCode="#,##0\ &quot;€&quot;;[Red]\-#,##0\ &quot;€&quot;"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -206,7 +212,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -220,7 +226,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -229,6 +235,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -543,7 +552,7 @@
     <col min="1" max="1" width="12.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
     <col min="3" max="3" width="28.77734375" customWidth="1"/>
-    <col min="4" max="4" width="40.109375" customWidth="1"/>
+    <col min="4" max="4" width="55" customWidth="1"/>
     <col min="5" max="5" width="42.109375" customWidth="1"/>
     <col min="6" max="6" width="15.6640625" customWidth="1"/>
     <col min="7" max="7" width="40.6640625" customWidth="1"/>
@@ -603,8 +612,12 @@
       <c r="C3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
+      <c r="D3" s="5">
+        <v>250</v>
+      </c>
+      <c r="E3" s="5">
+        <v>10</v>
+      </c>
       <c r="F3" s="3" t="s">
         <v>9</v>
       </c>
@@ -628,8 +641,12 @@
       <c r="C4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
+      <c r="D4" s="5">
+        <v>250</v>
+      </c>
+      <c r="E4" s="5">
+        <v>10</v>
+      </c>
       <c r="F4" s="3" t="s">
         <v>9</v>
       </c>
@@ -653,8 +670,12 @@
       <c r="C5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
+      <c r="D5" s="5">
+        <v>250</v>
+      </c>
+      <c r="E5" s="5">
+        <v>10</v>
+      </c>
       <c r="F5" s="3" t="s">
         <v>9</v>
       </c>
@@ -678,8 +699,12 @@
       <c r="C6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
+      <c r="D6" s="5">
+        <v>250</v>
+      </c>
+      <c r="E6" s="5">
+        <v>10</v>
+      </c>
       <c r="F6" s="3" t="s">
         <v>9</v>
       </c>
@@ -703,8 +728,12 @@
       <c r="C7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
+      <c r="D7" s="5">
+        <v>250</v>
+      </c>
+      <c r="E7" s="5">
+        <v>10</v>
+      </c>
       <c r="F7" s="3" t="s">
         <v>9</v>
       </c>
@@ -728,8 +757,12 @@
       <c r="C8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
+      <c r="D8" s="5">
+        <v>250</v>
+      </c>
+      <c r="E8" s="5">
+        <v>10</v>
+      </c>
       <c r="F8" s="3" t="s">
         <v>9</v>
       </c>
@@ -753,8 +786,12 @@
       <c r="C9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
+      <c r="D9" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="5">
+        <v>15</v>
+      </c>
       <c r="F9" s="3" t="s">
         <v>9</v>
       </c>
@@ -778,8 +815,12 @@
       <c r="C10" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
+      <c r="D10" s="5">
+        <v>250</v>
+      </c>
+      <c r="E10" s="5">
+        <v>10</v>
+      </c>
       <c r="F10" s="3" t="s">
         <v>9</v>
       </c>
@@ -803,8 +844,12 @@
       <c r="C11" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
+      <c r="D11" s="5">
+        <v>250</v>
+      </c>
+      <c r="E11" s="5">
+        <v>10</v>
+      </c>
       <c r="F11" s="3" t="s">
         <v>9</v>
       </c>
@@ -828,8 +873,12 @@
       <c r="C12" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
+      <c r="D12" s="5">
+        <v>250</v>
+      </c>
+      <c r="E12" s="5">
+        <v>10</v>
+      </c>
       <c r="F12" s="3" t="s">
         <v>9</v>
       </c>
